--- a/Mataquito/supplemental/Table_S7.xlsx
+++ b/Mataquito/supplemental/Table_S7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/MataquitoWatershedAnalysis/Mataquito/supplemental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5473FC-7A7D-9347-BD96-A0881269BDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A213F2-FF0E-814F-8691-D4FDDDA4D454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Part A. Sediment budget at CT-9 (PC = CT-8.2 configuration)</t>
   </si>
@@ -58,6 +58,12 @@
     <t>Principal Cordillera parents (E_CT-5 A_CT-5 + E_CT-6 A_CT-6)</t>
   </si>
   <si>
+    <t>Teno, CT-5 (E_CT-5 A_CT-5)</t>
+  </si>
+  <si>
+    <t>Lontué, CT-6 (E_CT-6 A_CT-6)</t>
+  </si>
+  <si>
     <t>Central Depression (transfer zone)</t>
   </si>
   <si>
@@ -110,6 +116,9 @@
   </si>
   <si>
     <t>Coastal Cordillera (CT-3*)</t>
+  </si>
+  <si>
+    <t>Teno share of Principal Cordillera parent flux</t>
   </si>
   <si>
     <t>Part B. Mineral flux ratios, parent A / parent B (zircon from V_max mixing)</t>
@@ -518,30 +527,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="46.1640625" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="8" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -552,7 +571,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -563,7 +582,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -574,22 +593,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -603,117 +621,116 @@
         <v>722.8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>618.79999999999995</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>591.70000000000005</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>645.79999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>36.5</v>
+        <v>76.7</v>
       </c>
       <c r="C10">
-        <v>34.5</v>
+        <v>72.5</v>
       </c>
       <c r="D10">
-        <v>38.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>80.900000000000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>732.1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>704.4</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>759.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>650</v>
+        <v>36.5</v>
       </c>
       <c r="C12">
-        <v>614.1</v>
+        <v>34.5</v>
       </c>
       <c r="D12">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
+        <v>732.1</v>
+      </c>
+      <c r="C13">
+        <v>704.4</v>
+      </c>
+      <c r="D13">
+        <v>759.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>650</v>
+      </c>
+      <c r="C14">
+        <v>614.1</v>
+      </c>
+      <c r="D14">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
         <v>734.6</v>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>706.9</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>762</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16">
-        <v>118.3</v>
-      </c>
-      <c r="C16">
-        <v>113.8</v>
-      </c>
-      <c r="D16">
-        <v>122.7</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
         <v>22</v>
-      </c>
-      <c r="B17">
-        <v>170.9</v>
-      </c>
-      <c r="C17">
-        <v>164.2</v>
-      </c>
-      <c r="D17">
-        <v>177.6</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -721,326 +738,367 @@
         <v>23</v>
       </c>
       <c r="B18">
+        <v>118.3</v>
+      </c>
+      <c r="C18">
+        <v>113.8</v>
+      </c>
+      <c r="D18">
+        <v>122.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
+        <v>170.9</v>
+      </c>
+      <c r="C19">
+        <v>164.2</v>
+      </c>
+      <c r="D19">
+        <v>177.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
         <v>29.5</v>
       </c>
-      <c r="C18">
+      <c r="C20">
         <v>27.9</v>
       </c>
-      <c r="D18">
+      <c r="D20">
         <v>31.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="64" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21">
-        <v>95</v>
-      </c>
-      <c r="C21">
-        <v>94.7</v>
-      </c>
-      <c r="D21">
-        <v>95.3</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
         <v>29</v>
       </c>
-      <c r="B22">
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23">
+        <v>95</v>
+      </c>
+      <c r="C23">
+        <v>94.7</v>
+      </c>
+      <c r="D23">
+        <v>95.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
         <v>5</v>
       </c>
-      <c r="C22">
+      <c r="C24">
         <v>4.7</v>
       </c>
-      <c r="D22">
+      <c r="D24">
         <v>5.3</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="96" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="B25">
+        <v>89</v>
+      </c>
+      <c r="C25">
+        <v>88.3</v>
+      </c>
+      <c r="D25">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="1" t="s">
+    </row>
+    <row r="28" spans="1:16" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="B28" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="L28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B26" t="s">
+      <c r="M28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C26">
-        <v>28.5</v>
-      </c>
-      <c r="D26">
-        <v>22</v>
-      </c>
-      <c r="E26">
-        <v>38.299999999999997</v>
-      </c>
-      <c r="F26">
-        <v>96.6</v>
-      </c>
-      <c r="G26">
-        <v>95.7</v>
-      </c>
-      <c r="H26">
-        <v>97.5</v>
-      </c>
-      <c r="I26">
-        <v>1.76</v>
-      </c>
-      <c r="J26">
-        <v>1.2</v>
-      </c>
-      <c r="K26">
-        <v>2.52</v>
-      </c>
-      <c r="L26">
-        <v>63.8</v>
-      </c>
-      <c r="M26">
-        <v>54.6</v>
-      </c>
-      <c r="N26">
-        <v>71.599999999999994</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="N28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C27">
-        <v>60.6</v>
-      </c>
-      <c r="D27">
-        <v>41</v>
-      </c>
-      <c r="E27">
-        <v>104</v>
-      </c>
-      <c r="F27">
-        <v>98.4</v>
-      </c>
-      <c r="G27">
-        <v>97.6</v>
-      </c>
-      <c r="H27">
-        <v>99</v>
-      </c>
-      <c r="I27">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="J27">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K27">
-        <v>1.25</v>
-      </c>
-      <c r="L27">
-        <v>45.9</v>
-      </c>
-      <c r="M27">
-        <v>35.5</v>
-      </c>
-      <c r="N27">
-        <v>55.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="D28">
-        <v>28.8</v>
-      </c>
-      <c r="E28">
-        <v>58</v>
-      </c>
-      <c r="F28">
-        <v>97.5</v>
-      </c>
-      <c r="G28">
-        <v>96.6</v>
-      </c>
-      <c r="H28">
-        <v>98.3</v>
-      </c>
-      <c r="I28">
-        <v>1.25</v>
-      </c>
-      <c r="J28">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="K28">
-        <v>1.71</v>
-      </c>
-      <c r="L28">
-        <v>55.6</v>
-      </c>
-      <c r="M28">
-        <v>47.2</v>
-      </c>
-      <c r="N28">
-        <v>63.1</v>
-      </c>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
         <v>49</v>
       </c>
-      <c r="B29" t="s">
-        <v>50</v>
-      </c>
       <c r="C29">
-        <v>0.60699999999999998</v>
+        <v>28.5</v>
       </c>
       <c r="D29">
-        <v>0.42299999999999999</v>
+        <v>22</v>
       </c>
       <c r="E29">
-        <v>0.81399999999999995</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="F29">
-        <v>37.799999999999997</v>
+        <v>96.6</v>
       </c>
       <c r="G29">
-        <v>29.7</v>
+        <v>95.7</v>
       </c>
       <c r="H29">
-        <v>44.9</v>
+        <v>97.5</v>
       </c>
       <c r="I29">
-        <v>4.63</v>
+        <v>1.76</v>
       </c>
       <c r="J29">
-        <v>3.94</v>
+        <v>1.2</v>
       </c>
       <c r="K29">
-        <v>5.61</v>
+        <v>2.52</v>
       </c>
       <c r="L29">
-        <v>82.2</v>
+        <v>63.8</v>
       </c>
       <c r="M29">
-        <v>79.8</v>
+        <v>54.6</v>
       </c>
       <c r="N29">
-        <v>84.9</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30">
+        <v>60.6</v>
+      </c>
+      <c r="D30">
+        <v>41</v>
+      </c>
+      <c r="E30">
+        <v>104</v>
+      </c>
+      <c r="F30">
+        <v>98.4</v>
+      </c>
+      <c r="G30">
+        <v>97.6</v>
+      </c>
+      <c r="H30">
+        <v>99</v>
+      </c>
+      <c r="I30">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="J30">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K30">
+        <v>1.25</v>
+      </c>
+      <c r="L30">
+        <v>45.9</v>
+      </c>
+      <c r="M30">
+        <v>35.5</v>
+      </c>
+      <c r="N30">
+        <v>55.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
         <v>51</v>
       </c>
-      <c r="C30">
+      <c r="C31">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="D31">
+        <v>28.8</v>
+      </c>
+      <c r="E31">
+        <v>58</v>
+      </c>
+      <c r="F31">
+        <v>97.5</v>
+      </c>
+      <c r="G31">
+        <v>96.6</v>
+      </c>
+      <c r="H31">
+        <v>98.3</v>
+      </c>
+      <c r="I31">
+        <v>1.25</v>
+      </c>
+      <c r="J31">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="K31">
+        <v>1.71</v>
+      </c>
+      <c r="L31">
+        <v>55.6</v>
+      </c>
+      <c r="M31">
+        <v>47.2</v>
+      </c>
+      <c r="N31">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="D32">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="E32">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="F32">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="G32">
+        <v>29.7</v>
+      </c>
+      <c r="H32">
+        <v>44.9</v>
+      </c>
+      <c r="I32">
+        <v>4.63</v>
+      </c>
+      <c r="J32">
+        <v>3.94</v>
+      </c>
+      <c r="K32">
+        <v>5.61</v>
+      </c>
+      <c r="L32">
+        <v>82.2</v>
+      </c>
+      <c r="M32">
+        <v>79.8</v>
+      </c>
+      <c r="N32">
+        <v>84.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33">
         <v>1.06</v>
       </c>
-      <c r="D30">
+      <c r="D33">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E30">
+      <c r="E33">
         <v>1.36</v>
       </c>
-      <c r="F30">
+      <c r="F33">
         <v>51.5</v>
       </c>
-      <c r="G30">
+      <c r="G33">
         <v>44.7</v>
       </c>
-      <c r="H30">
+      <c r="H33">
         <v>57.6</v>
       </c>
-      <c r="I30">
+      <c r="I33">
         <v>6.8</v>
       </c>
-      <c r="J30">
+      <c r="J33">
         <v>4.72</v>
       </c>
-      <c r="K30">
+      <c r="K33">
         <v>10.4</v>
       </c>
-      <c r="L30">
+      <c r="L33">
         <v>87.2</v>
       </c>
-      <c r="M30">
+      <c r="M33">
         <v>82.5</v>
       </c>
-      <c r="N30">
+      <c r="N33">
         <v>91.2</v>
       </c>
     </row>
